--- a/jogos_2025-03-25.xlsx
+++ b/jogos_2025-03-25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="76">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -223,15 +169,15 @@
     <t>Carlisle United</t>
   </si>
   <si>
+    <t>Bayelsa United</t>
+  </si>
+  <si>
+    <t>Abia Warriors</t>
+  </si>
+  <si>
     <t>Kwara United</t>
   </si>
   <si>
-    <t>Bayelsa United</t>
-  </si>
-  <si>
-    <t>Abia Warriors</t>
-  </si>
-  <si>
     <t>Cerro Largo</t>
   </si>
   <si>
@@ -247,15 +193,15 @@
     <t>Milton Keynes Dons</t>
   </si>
   <si>
+    <t>Rivers United</t>
+  </si>
+  <si>
+    <t>Lobi Stars</t>
+  </si>
+  <si>
     <t>Nasarawa United</t>
   </si>
   <si>
-    <t>Rivers United</t>
-  </si>
-  <si>
-    <t>Lobi Stars</t>
-  </si>
-  <si>
     <t>Torque</t>
   </si>
   <si>
@@ -274,13 +220,13 @@
     <t>['26', '45+4']</t>
   </si>
   <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['24', '90+3']</t>
+  </si>
+  <si>
     <t>['64']</t>
-  </si>
-  <si>
-    <t>['19']</t>
-  </si>
-  <si>
-    <t>['24', '90+3']</t>
   </si>
   <si>
     <t>['47']</t>
@@ -659,10 +605,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD9"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -777,79 +723,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45741</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -864,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L2">
         <v>2.15</v>
@@ -939,87 +831,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="AK2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AL2">
-        <v>1.28</v>
-      </c>
-      <c r="AM2">
-        <v>1.28</v>
-      </c>
-      <c r="AN2">
-        <v>1.67</v>
-      </c>
-      <c r="AO2">
-        <v>9</v>
-      </c>
-      <c r="AP2">
-        <v>1.27</v>
-      </c>
-      <c r="AQ2">
-        <v>1.48</v>
-      </c>
-      <c r="AR2">
-        <v>1.77</v>
-      </c>
-      <c r="AS2">
-        <v>2.2</v>
-      </c>
-      <c r="AT2">
-        <v>2.8</v>
-      </c>
-      <c r="AU2">
-        <v>3.3</v>
-      </c>
-      <c r="AV2">
-        <v>2.45</v>
-      </c>
-      <c r="AW2">
-        <v>1.92</v>
-      </c>
-      <c r="AX2">
-        <v>1.58</v>
-      </c>
-      <c r="AY2">
-        <v>1.38</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.73</v>
-      </c>
-      <c r="BC2">
-        <v>2.5</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45741.6875</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45741</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1034,7 +872,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L3">
         <v>2.55</v>
@@ -1109,87 +947,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ3" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AL3">
-        <v>1.4</v>
-      </c>
-      <c r="AM3">
-        <v>1.3</v>
-      </c>
-      <c r="AN3">
-        <v>1.5</v>
-      </c>
-      <c r="AO3">
-        <v>5</v>
-      </c>
-      <c r="AP3">
-        <v>1.3</v>
-      </c>
-      <c r="AQ3">
-        <v>1.53</v>
-      </c>
-      <c r="AR3">
-        <v>1.85</v>
-      </c>
-      <c r="AS3">
-        <v>2.33</v>
-      </c>
-      <c r="AT3">
-        <v>3.05</v>
-      </c>
-      <c r="AU3">
-        <v>3</v>
-      </c>
-      <c r="AV3">
-        <v>2.25</v>
-      </c>
-      <c r="AW3">
-        <v>1.79</v>
-      </c>
-      <c r="AX3">
-        <v>1.49</v>
-      </c>
-      <c r="AY3">
-        <v>1.3</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.91</v>
-      </c>
-      <c r="BC3">
-        <v>2.2</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>73</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45741.69791666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45741</v>
       </c>
       <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
         <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" t="s">
-        <v>75</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1204,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L4">
         <v>3.2</v>
@@ -1279,87 +1063,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ4" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="AK4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL4">
-        <v>1.73</v>
-      </c>
-      <c r="AM4">
-        <v>1.25</v>
-      </c>
-      <c r="AN4">
-        <v>1.28</v>
-      </c>
-      <c r="AO4">
-        <v>5</v>
-      </c>
-      <c r="AP4">
-        <v>1.26</v>
-      </c>
-      <c r="AQ4">
-        <v>1.46</v>
-      </c>
-      <c r="AR4">
-        <v>1.76</v>
-      </c>
-      <c r="AS4">
-        <v>2.2</v>
-      </c>
-      <c r="AT4">
-        <v>2.85</v>
-      </c>
-      <c r="AU4">
-        <v>3.25</v>
-      </c>
-      <c r="AV4">
-        <v>2.4</v>
-      </c>
-      <c r="AW4">
-        <v>1.88</v>
-      </c>
-      <c r="AX4">
-        <v>1.55</v>
-      </c>
-      <c r="AY4">
-        <v>1.34</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.45</v>
-      </c>
-      <c r="BC4">
-        <v>1.77</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>64</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45741.69791666666</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45741</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1374,7 +1104,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L5">
         <v>2.52</v>
@@ -1449,87 +1179,33 @@
         <v>1.12</v>
       </c>
       <c r="AJ5" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="AK5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL5">
-        <v>1.62</v>
-      </c>
-      <c r="AM5">
-        <v>1.25</v>
-      </c>
-      <c r="AN5">
-        <v>1.36</v>
-      </c>
-      <c r="AO5">
-        <v>9</v>
-      </c>
-      <c r="AP5">
-        <v>1.41</v>
-      </c>
-      <c r="AQ5">
-        <v>1.68</v>
-      </c>
-      <c r="AR5">
-        <v>2.1</v>
-      </c>
-      <c r="AS5">
-        <v>2.7</v>
-      </c>
-      <c r="AT5">
-        <v>3.55</v>
-      </c>
-      <c r="AU5">
-        <v>2.65</v>
-      </c>
-      <c r="AV5">
-        <v>2.02</v>
-      </c>
-      <c r="AW5">
-        <v>1.65</v>
-      </c>
-      <c r="AX5">
-        <v>1.4</v>
-      </c>
-      <c r="AY5">
-        <v>1.24</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>2.25</v>
-      </c>
-      <c r="BC5">
-        <v>1.73</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>74</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45741.69791666666</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45741</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1538,79 +1214,79 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="M6">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>3.41</v>
       </c>
       <c r="O6">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="P6">
-        <v>6.55</v>
+        <v>5.7</v>
       </c>
       <c r="Q6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R6">
+        <v>1.55</v>
+      </c>
+      <c r="S6">
+        <v>2.1</v>
+      </c>
+      <c r="T6">
+        <v>4.1</v>
+      </c>
+      <c r="U6">
+        <v>1.16</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>1.08</v>
+      </c>
+      <c r="Y6">
+        <v>5.7</v>
+      </c>
+      <c r="Z6">
         <v>1.57</v>
       </c>
-      <c r="S6">
-        <v>2.26</v>
-      </c>
-      <c r="T6">
-        <v>3.84</v>
-      </c>
-      <c r="U6">
-        <v>1.18</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>1.05</v>
-      </c>
-      <c r="Y6">
-        <v>6.55</v>
-      </c>
-      <c r="Z6">
-        <v>1.52</v>
-      </c>
       <c r="AA6">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB6">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC6">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AD6">
-        <v>5.45</v>
+        <v>6.15</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>2.98</v>
+        <v>2.57</v>
       </c>
       <c r="AG6">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1619,90 +1295,36 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="AK6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL6">
-        <v>1</v>
-      </c>
-      <c r="AM6">
-        <v>1.21</v>
-      </c>
-      <c r="AN6">
-        <v>2.57</v>
-      </c>
-      <c r="AO6">
-        <v>9</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.33</v>
-      </c>
-      <c r="BC6">
-        <v>5</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>64</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45741.83333333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45741</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1714,237 +1336,183 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L7">
+        <v>1.2</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>12</v>
+      </c>
+      <c r="O7">
+        <v>1.14</v>
+      </c>
+      <c r="P7">
+        <v>9.1</v>
+      </c>
+      <c r="Q7">
+        <v>7.5</v>
+      </c>
+      <c r="R7">
+        <v>1.42</v>
+      </c>
+      <c r="S7">
+        <v>2.58</v>
+      </c>
+      <c r="T7">
+        <v>2.84</v>
+      </c>
+      <c r="U7">
+        <v>1.35</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7">
+        <v>1.09</v>
+      </c>
+      <c r="X7">
+        <v>1.06</v>
+      </c>
+      <c r="Y7">
+        <v>7.2</v>
+      </c>
+      <c r="Z7">
+        <v>1.25</v>
+      </c>
+      <c r="AA7">
+        <v>3.28</v>
+      </c>
+      <c r="AB7">
         <v>1.9</v>
       </c>
-      <c r="M7">
-        <v>3.02</v>
-      </c>
-      <c r="N7">
-        <v>3.41</v>
-      </c>
-      <c r="O7">
-        <v>1.67</v>
-      </c>
-      <c r="P7">
-        <v>5.7</v>
-      </c>
-      <c r="Q7">
-        <v>3</v>
-      </c>
-      <c r="R7">
-        <v>1.55</v>
-      </c>
-      <c r="S7">
-        <v>2.1</v>
-      </c>
-      <c r="T7">
-        <v>4.1</v>
-      </c>
-      <c r="U7">
-        <v>1.16</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>1.08</v>
-      </c>
-      <c r="Y7">
-        <v>5.7</v>
-      </c>
-      <c r="Z7">
-        <v>1.57</v>
-      </c>
-      <c r="AA7">
-        <v>2.05</v>
-      </c>
-      <c r="AB7">
-        <v>3.1</v>
-      </c>
       <c r="AC7">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AD7">
-        <v>6.15</v>
+        <v>3.05</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AF7">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="AG7">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ7" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="AK7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL7">
-        <v>1.15</v>
-      </c>
-      <c r="AM7">
-        <v>1.25</v>
-      </c>
-      <c r="AN7">
-        <v>1.95</v>
-      </c>
-      <c r="AO7">
-        <v>12</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.67</v>
-      </c>
-      <c r="BC7">
-        <v>3</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>64</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45741.83333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45741</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
         <v>61</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
         <v>63</v>
       </c>
-      <c r="E8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>81</v>
-      </c>
       <c r="L8">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
+        <v>3.6</v>
+      </c>
+      <c r="N8">
+        <v>7</v>
+      </c>
+      <c r="O8">
+        <v>1.33</v>
+      </c>
+      <c r="P8">
+        <v>6.55</v>
+      </c>
+      <c r="Q8">
         <v>5</v>
       </c>
-      <c r="N8">
-        <v>12</v>
-      </c>
-      <c r="O8">
-        <v>1.14</v>
-      </c>
-      <c r="P8">
-        <v>9.1</v>
-      </c>
-      <c r="Q8">
-        <v>7.5</v>
-      </c>
       <c r="R8">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S8">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="T8">
-        <v>2.84</v>
+        <v>3.84</v>
       </c>
       <c r="U8">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>7.2</v>
+        <v>6.55</v>
       </c>
       <c r="Z8">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AA8">
-        <v>3.28</v>
+        <v>2.35</v>
       </c>
       <c r="AB8">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AC8">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AD8">
-        <v>3.05</v>
+        <v>5.45</v>
       </c>
       <c r="AE8">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
         <v>2.98</v>
@@ -1953,93 +1521,39 @@
         <v>1.32</v>
       </c>
       <c r="AH8">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="AK8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL8">
-        <v>1.01</v>
-      </c>
-      <c r="AM8">
-        <v>1.1</v>
-      </c>
-      <c r="AN8">
-        <v>3.68</v>
-      </c>
-      <c r="AO8">
-        <v>13</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.14</v>
-      </c>
-      <c r="BC8">
-        <v>7.5</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>64</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45741.83333333334</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45741</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
         <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" t="s">
-        <v>80</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2054,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="L9">
         <v>2.89</v>
@@ -2129,66 +1643,12 @@
         <v>1.15</v>
       </c>
       <c r="AJ9" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="AK9" t="s">
-        <v>93</v>
-      </c>
-      <c r="AL9">
-        <v>1.46</v>
-      </c>
-      <c r="AM9">
-        <v>1.29</v>
-      </c>
-      <c r="AN9">
-        <v>1.51</v>
-      </c>
-      <c r="AO9">
-        <v>7</v>
-      </c>
-      <c r="AP9">
-        <v>1.4</v>
-      </c>
-      <c r="AQ9">
-        <v>1.68</v>
-      </c>
-      <c r="AR9">
-        <v>2.07</v>
-      </c>
-      <c r="AS9">
-        <v>2.65</v>
-      </c>
-      <c r="AT9">
-        <v>3.55</v>
-      </c>
-      <c r="AU9">
-        <v>2.7</v>
-      </c>
-      <c r="AV9">
-        <v>2.05</v>
-      </c>
-      <c r="AW9">
-        <v>1.66</v>
-      </c>
-      <c r="AX9">
-        <v>1.41</v>
-      </c>
-      <c r="AY9">
-        <v>1.24</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>2.2</v>
-      </c>
-      <c r="BC9">
-        <v>1.73</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>75</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45741.83333333334</v>
       </c>
     </row>

--- a/jogos_2025-03-25.xlsx
+++ b/jogos_2025-03-25.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Carlisle United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['31', '63', '75']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['11', '20', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['26', '45+4']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['6', '37']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45741.69791666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Carlisle United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="M5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['26', '45+4']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['6', '37']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['31', '63', '75']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['11', '20', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45741.69791666666</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>3.41</v>
       </c>
       <c r="O6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S6" t="n">
         <v>2.1</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.57</v>
-      </c>
       <c r="AI6" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45741.83333333334</v>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Cerro Largo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>2.89</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>2.39</v>
       </c>
       <c r="O7" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.98</v>
+        <v>1.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.32</v>
+        <v>2.63</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['24', '90+3']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.68</v>
+        <v>1.51</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45741.83333333334</v>
@@ -1407,29 +1407,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cerro Largo</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.89</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>2.39</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="T8" t="n">
-        <v>2.25</v>
+        <v>3.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>5.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.44</v>
+        <v>2.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.63</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.46</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.51</v>
+        <v>2.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45741.83333333334</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1572,65 +1572,65 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.9</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.15</v>
+        <v>3.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['24', '90+3']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.95</v>
+        <v>3.68</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45741.83333333334</v>
